--- a/experiments/results/summary/compare_results.xlsx
+++ b/experiments/results/summary/compare_results.xlsx
@@ -495,13 +495,13 @@
         <v>98</v>
       </c>
       <c r="C4" t="n">
-        <v>99.40000000000001</v>
+        <v>99.2</v>
       </c>
       <c r="D4" s="1" t="n">
         <v>98</v>
       </c>
       <c r="E4" t="n">
-        <v>99.2</v>
+        <v>99.40000000000001</v>
       </c>
     </row>
     <row r="5">
@@ -530,16 +530,16 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="C6" t="n">
-        <v>160.6</v>
+        <v>160.5</v>
       </c>
       <c r="D6" s="1" t="n">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="E6" t="n">
-        <v>159.6</v>
+        <v>157.6</v>
       </c>
     </row>
     <row r="7">
@@ -549,16 +549,16 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>223</v>
+        <v>194</v>
       </c>
       <c r="C7" t="n">
-        <v>226</v>
+        <v>197.6</v>
       </c>
       <c r="D7" s="1" t="n">
-        <v>220</v>
+        <v>191</v>
       </c>
       <c r="E7" t="n">
-        <v>224.4</v>
+        <v>194.7</v>
       </c>
     </row>
     <row r="8">
@@ -567,11 +567,11 @@
           <t>WIP-FMS_07</t>
         </is>
       </c>
-      <c r="B8" s="1" t="n">
-        <v>233</v>
+      <c r="B8" t="n">
+        <v>234</v>
       </c>
       <c r="C8" t="n">
-        <v>236.8</v>
+        <v>236.6</v>
       </c>
       <c r="D8" s="1" t="n">
         <v>233</v>
@@ -586,17 +586,17 @@
           <t>WIP-FMS_08</t>
         </is>
       </c>
-      <c r="B9" t="n">
-        <v>238</v>
+      <c r="B9" s="1" t="n">
+        <v>198</v>
       </c>
       <c r="C9" t="n">
-        <v>241.2</v>
-      </c>
-      <c r="D9" s="1" t="n">
-        <v>237</v>
+        <v>203</v>
+      </c>
+      <c r="D9" t="n">
+        <v>200</v>
       </c>
       <c r="E9" t="n">
-        <v>239.5</v>
+        <v>202.4</v>
       </c>
     </row>
     <row r="10">
@@ -606,16 +606,16 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="C10" t="n">
-        <v>238.1</v>
+        <v>236.3</v>
       </c>
       <c r="D10" s="1" t="n">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="E10" t="n">
-        <v>236.3</v>
+        <v>236.2</v>
       </c>
     </row>
     <row r="11">
@@ -625,16 +625,16 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>252</v>
+        <v>265</v>
       </c>
       <c r="C11" t="n">
-        <v>255.9</v>
+        <v>269.9</v>
       </c>
       <c r="D11" s="1" t="n">
-        <v>245</v>
+        <v>264</v>
       </c>
       <c r="E11" t="n">
-        <v>253.8</v>
+        <v>267.3</v>
       </c>
     </row>
     <row r="12">
@@ -663,16 +663,16 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>318</v>
+        <v>331</v>
       </c>
       <c r="C13" t="n">
-        <v>324.3</v>
+        <v>339.7</v>
       </c>
       <c r="D13" s="1" t="n">
-        <v>304</v>
+        <v>321</v>
       </c>
       <c r="E13" t="n">
-        <v>313.2</v>
+        <v>331.4</v>
       </c>
     </row>
     <row r="14">
@@ -681,17 +681,17 @@
           <t>WIP-FMS_13</t>
         </is>
       </c>
-      <c r="B14" s="1" t="n">
-        <v>410</v>
+      <c r="B14" t="n">
+        <v>363</v>
       </c>
       <c r="C14" t="n">
-        <v>417.6</v>
+        <v>369.6</v>
       </c>
       <c r="D14" s="1" t="n">
-        <v>410</v>
+        <v>358</v>
       </c>
       <c r="E14" t="n">
-        <v>418.7</v>
+        <v>366.8</v>
       </c>
     </row>
     <row r="15">
@@ -701,16 +701,16 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>399</v>
+        <v>406</v>
       </c>
       <c r="C15" t="n">
-        <v>406.4</v>
+        <v>409.2</v>
       </c>
       <c r="D15" s="1" t="n">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="E15" t="n">
-        <v>402.5</v>
+        <v>404.9</v>
       </c>
     </row>
     <row r="16">
@@ -719,17 +719,17 @@
           <t>WIP-FMS_15</t>
         </is>
       </c>
-      <c r="B16" t="n">
-        <v>392</v>
+      <c r="B16" s="1" t="n">
+        <v>456</v>
       </c>
       <c r="C16" t="n">
-        <v>400.8</v>
+        <v>483</v>
       </c>
       <c r="D16" s="1" t="n">
-        <v>388</v>
+        <v>456</v>
       </c>
       <c r="E16" t="n">
-        <v>397.1</v>
+        <v>477.2</v>
       </c>
     </row>
     <row r="17">
@@ -739,16 +739,16 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>436</v>
+        <v>371</v>
       </c>
       <c r="C17" t="n">
-        <v>441.3</v>
+        <v>377.6</v>
       </c>
       <c r="D17" s="1" t="n">
-        <v>425</v>
+        <v>368</v>
       </c>
       <c r="E17" t="n">
-        <v>434.1</v>
+        <v>372.6</v>
       </c>
     </row>
     <row r="18">
@@ -757,17 +757,17 @@
           <t>WIP-FMS_17</t>
         </is>
       </c>
-      <c r="B18" t="n">
-        <v>429</v>
+      <c r="B18" s="1" t="n">
+        <v>431</v>
       </c>
       <c r="C18" t="n">
-        <v>443.5</v>
-      </c>
-      <c r="D18" s="1" t="n">
-        <v>428</v>
+        <v>440.8</v>
+      </c>
+      <c r="D18" t="n">
+        <v>435</v>
       </c>
       <c r="E18" t="n">
-        <v>439.1</v>
+        <v>441.5</v>
       </c>
     </row>
     <row r="19">
@@ -777,16 +777,16 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>431</v>
+        <v>513</v>
       </c>
       <c r="C19" t="n">
-        <v>440.3</v>
+        <v>526.2</v>
       </c>
       <c r="D19" s="1" t="n">
-        <v>428</v>
+        <v>502</v>
       </c>
       <c r="E19" t="n">
-        <v>432.9</v>
+        <v>513.5</v>
       </c>
     </row>
     <row r="20">
@@ -795,17 +795,17 @@
           <t>WIP-FMS_19</t>
         </is>
       </c>
-      <c r="B20" t="n">
-        <v>430</v>
+      <c r="B20" s="1" t="n">
+        <v>495</v>
       </c>
       <c r="C20" t="n">
-        <v>440.4</v>
-      </c>
-      <c r="D20" s="1" t="n">
-        <v>428</v>
+        <v>506.9</v>
+      </c>
+      <c r="D20" t="n">
+        <v>497</v>
       </c>
       <c r="E20" t="n">
-        <v>433.8</v>
+        <v>504.9</v>
       </c>
     </row>
     <row r="21">
@@ -814,17 +814,17 @@
           <t>WIP-FMS_20</t>
         </is>
       </c>
-      <c r="B21" t="n">
-        <v>434</v>
+      <c r="B21" s="1" t="n">
+        <v>435</v>
       </c>
       <c r="C21" t="n">
-        <v>437.5</v>
-      </c>
-      <c r="D21" s="1" t="n">
-        <v>425</v>
+        <v>460.4</v>
+      </c>
+      <c r="D21" t="n">
+        <v>440</v>
       </c>
       <c r="E21" t="n">
-        <v>433.9</v>
+        <v>453.8</v>
       </c>
     </row>
   </sheetData>
